--- a/output/details/2026-05-11/preprocessed_data.xlsx
+++ b/output/details/2026-05-11/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46153</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1080747072273343</v>
+        <v>-0.107717721760058</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2007135019372363</v>
+        <v>-0.1302098175780377</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2004237806969356</v>
+        <v>-0.1299501045089472</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1329204034379483</v>
+        <v>0.01411696036532211</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703676015923557</v>
+        <v>0.001703955153260658</v>
       </c>
       <c r="G2" t="n">
-        <v>1.777639739337304</v>
+        <v>2.352573767902122</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4610075137377472</v>
+        <v>-0.2571187436036702</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
